--- a/data/trans_orig/IQ17A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ17A-Edad-trans_orig.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>14718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32710</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40050</t>
+          <t>40034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>38074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67561</t>
+          <t>67472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77051</t>
+          <t>76810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -2326,47 +2326,47 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>681</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5548</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>487</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43216</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48533</t>
+          <t>48539</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51655</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58533</t>
+          <t>58998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97743</t>
+          <t>97835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106147</t>
+          <t>106537</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3331,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>19616</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25489</t>
+          <t>25504</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>37827</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>44601</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -4523,12 +4523,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>41975</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49179</t>
+          <t>49266</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5341,12 +5341,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5376,12 +5376,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5417,12 +5417,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5467,47 +5467,47 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>20384</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>13854</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>27760</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
           <t>9,52%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>20384</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>14235</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>28200</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>112530</t>
+          <t>113352</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>122943</t>
+          <t>123541</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>137939</t>
+          <t>137779</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>150775</t>
+          <t>150836</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>255165</t>
+          <t>256012</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>271096</t>
+          <t>271506</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6543,12 +6543,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>15355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -6765,12 +6765,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>45833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>54860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38820</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>49328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88822</t>
+          <t>88055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102097</t>
+          <t>102456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>24202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41907</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50371</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48971</t>
+          <t>49348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59154</t>
+          <t>59477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94299</t>
+          <t>94280</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107408</t>
+          <t>106988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -8664,12 +8664,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -8775,12 +8775,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44146</t>
+          <t>44013</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15044</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>34998</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>42457</t>
+          <t>42397</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10563,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10648,12 +10648,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10689,12 +10689,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17894</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -10785,12 +10785,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>131835</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>145161</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10800,12 +10800,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>129908</t>
+          <t>129320</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>146002</t>
+          <t>146589</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -10855,12 +10855,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>265711</t>
+          <t>265382</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>287091</t>
+          <t>287705</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -11911,12 +11911,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11981,12 +11981,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -12022,12 +12022,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33890</t>
+          <t>33828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41215</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>31108</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38839</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12092,12 +12092,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>67587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78285</t>
+          <t>78974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12107,12 +12107,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -12916,12 +12916,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12931,12 +12931,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36328</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42034</t>
+          <t>41974</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13042,12 +13042,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13062,12 +13062,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40492</t>
+          <t>40455</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47023</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13077,12 +13077,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13097,12 +13097,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79208</t>
+          <t>78809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87823</t>
+          <t>88133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13112,12 +13112,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -13921,12 +13921,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14006,12 +14006,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -14032,12 +14032,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31268</t>
+          <t>31358</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14047,12 +14047,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -14102,12 +14102,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58041</t>
+          <t>57959</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65587</t>
+          <t>65615</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -14926,12 +14926,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14996,12 +14996,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15011,12 +15011,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -15037,12 +15037,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>20340</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15052,12 +15052,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -15107,12 +15107,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -15890,12 +15890,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -15931,12 +15931,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -15946,12 +15946,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -15966,12 +15966,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -15981,12 +15981,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16001,12 +16001,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>36854</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16016,12 +16016,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -16042,12 +16042,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>117981</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>130442</t>
+          <t>130659</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16057,12 +16057,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16077,12 +16077,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>124903</t>
+          <t>124365</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>136089</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16112,12 +16112,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>246136</t>
+          <t>246342</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>263924</t>
+          <t>263065</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -16925,7 +16925,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -17168,12 +17168,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -17183,12 +17183,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -17238,12 +17238,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -17253,12 +17253,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -17294,12 +17294,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -17349,12 +17349,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27586</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -17364,12 +17364,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -17784,7 +17784,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -18097,12 +18097,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>533</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -18112,12 +18112,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -18132,12 +18132,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -18208,12 +18208,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>779</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -18223,12 +18223,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -18243,12 +18243,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -18258,12 +18258,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -18319,12 +18319,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>22742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>30361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -18334,12 +18334,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48489</t>
+          <t>48207</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57943</t>
+          <t>57819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -18369,12 +18369,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -18961,7 +18961,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -19183,7 +19183,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -19248,12 +19248,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>530</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -19263,12 +19263,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -19289,12 +19289,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>24976</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -19304,12 +19304,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -19324,12 +19324,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36364</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -19339,12 +19339,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -19359,12 +19359,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58467</t>
+          <t>58878</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66387</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -19374,12 +19374,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -19855,7 +19855,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -19870,7 +19870,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -20218,12 +20218,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>819</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20253,12 +20253,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -20309,7 +20309,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>34029</t>
+          <t>33647</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>41731</t>
+          <t>41727</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -20364,12 +20364,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>56872</t>
+          <t>57703</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>65583</t>
+          <t>66213</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -20379,12 +20379,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -20784,7 +20784,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -21112,12 +21112,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -21127,12 +21127,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21147,12 +21147,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -21188,12 +21188,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -21203,12 +21203,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21223,12 +21223,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -21238,12 +21238,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21258,12 +21258,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -21273,12 +21273,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -21299,12 +21299,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>96329</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -21314,12 +21314,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21334,12 +21334,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>123962</t>
+          <t>123834</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -21349,12 +21349,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21369,12 +21369,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>202958</t>
+          <t>203340</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>218419</t>
+          <t>217940</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -21384,12 +21384,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
